--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.3--20251211153003.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.3--20251211153003.xlsx
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>101</t>
+    <t>124</t>
   </si>
   <si>
     <t>Code</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.3--20251211153003.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.3--20251211153003.xlsx
@@ -502,61 +502,61 @@
     <t>2.16.840.1.113883.3.1937.777.24.5.3.57</t>
   </si>
   <si>
-    <t>Z2 Patientendaten erheben, nutzen, Kontaktierung im acribis-Projekt</t>
+    <t>Z2 PATDAT erheben nutzen kontakt (ACRIBIS)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.58</t>
   </si>
   <si>
-    <t>PATDAT erheben, nutzen, Kontaktierung im acribis-Projekt</t>
+    <t>PATDAT erheben nutzen kontakt (ACRIBIS)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.59</t>
   </si>
   <si>
-    <t>Z2 IDAT Melderegister abfragen, speichern, verarbeiten im acribis-Projekt</t>
+    <t>Z2 IDAT Melderegister abfragen speichern verarbeiten (ACRIBIS)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.60</t>
   </si>
   <si>
-    <t>Anschrift und Vitalstatus Melderegister abfragen, speichern, verarbeiten im acribis-Projekt</t>
+    <t>IDAT Melderegister abfragen speichern verarbeiten (ACRIBIS)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.61</t>
   </si>
   <si>
-    <t>Z2 MDAT Hausarzt erheben, speichern, verarbeiten, nutzen im acribis-Projekt</t>
+    <t>Z2 MDAT Hausarzt erheben speichern verarbeiten nutzen (ACRIBIS)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.62</t>
   </si>
   <si>
-    <t>MDAT Hausarzt erheben, speichern, verarbeiten, nutzen im acribis-Projekt</t>
+    <t>MDAT Hausarzt erheben speichern verarbeiten nutzen (ACRIBIS)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.63</t>
   </si>
   <si>
-    <t>Z3 PROMDAT Patientenbefragung</t>
+    <t>Z3 PROMDAT Patientenbefragung (PROM)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.64</t>
   </si>
   <si>
-    <t>PROMDAT Patientenbefragung erheben</t>
+    <t>PROMDAT Patientenbefragung erheben (PROM)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.65</t>
   </si>
   <si>
-    <t>PROMDAT wissenschaftlich nutzen</t>
+    <t>PROMDAT wissenschaftlich nutzen (PROM)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.66</t>
   </si>
   <si>
-    <t>Rekontaktierung PROM Studien</t>
+    <t>Rekontaktierung PROM Studien (PROM)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.67</t>
@@ -568,7 +568,7 @@
     <t>2.16.840.1.113883.3.1937.777.24.5.3.68</t>
   </si>
   <si>
-    <t>IDAT speichern, verabeiten (SNID)</t>
+    <t>IDAT speichern, verarbeiten (SNID)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.69</t>
@@ -610,7 +610,7 @@
     <t>2.16.840.1.113883.3.1937.777.24.5.3.75</t>
   </si>
   <si>
-    <t>BIOMAT Eigentum übertragen_NUM (SNID)</t>
+    <t>BIOMAT Eigentum übertragen NUM (SNID)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.76</t>
@@ -712,19 +712,19 @@
     <t>2.16.840.1.113883.3.1937.777.24.5.3.92</t>
   </si>
   <si>
-    <t>MDAT SNID bereitstellen Dritte</t>
+    <t>MDAT SNID bereitstellen Dritte (SNID)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.93</t>
   </si>
   <si>
-    <t>BIOMAT SNID bereitstellen Dritte</t>
+    <t>BIOMAT SNID bereitstellen Dritte (SNID)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.94</t>
   </si>
   <si>
-    <t>Z4 Rekontaktierung Patient (SNID)</t>
+    <t>Z4 Rekontaktierung Patient NU (SNID)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.95</t>
@@ -736,19 +736,19 @@
     <t>2.16.840.1.113883.3.1937.777.24.5.3.96</t>
   </si>
   <si>
-    <t>Z4_Rekontaktierung_FU</t>
+    <t>Z4 Rekontaktierung Patient weitere Studien (SNID)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.97</t>
   </si>
   <si>
-    <t>Rekontaktierung weitere Studien (SNID)</t>
+    <t>Rekontaktierung Patient weitere Studien (SNID)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.98</t>
   </si>
   <si>
-    <t>IDAT SNID bereitstellen OE</t>
+    <t>IDAT SNID bereitstellen OE (SNID)</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.99</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.3--20251211153003.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.3--20251211153003.xlsx
@@ -193,7 +193,7 @@
     <t>2.16.840.1.113883.3.1937.777.24.5.3.5</t>
   </si>
   <si>
-    <t xml:space="preserve">IDAT bereitstellen </t>
+    <t>IDAT bereitstellen</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.5.3.6</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.3--20251211153003.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-2.16.840.1.113883.3.1937.777.24.5.3--20251211153003.xlsx
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>124</t>
+    <t>101</t>
   </si>
   <si>
     <t>Code</t>
